--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -2307,22 +2307,22 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>87.47283768142248</v>
+        <v>87.56537469454608</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>99.10709529417855</v>
+        <v>99.48409928257496</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>106.6824907823649</v>
+        <v>106.9944391060197</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>114.8982326066757</v>
+        <v>115.0917272987826</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>130.1682181904347</v>
+        <v>131.1946500992745</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>0.55144</v>
+        <v>0.56294</v>
       </c>
     </row>
     <row r="6">
@@ -2332,22 +2332,22 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>78.29508034182929</v>
+        <v>79.1329359945467</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>96.93670208976819</v>
+        <v>97.94831820710576</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>109.9075824742194</v>
+        <v>110.42539731263</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>124.4581193266816</v>
+        <v>124.4873816166916</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>154.1934203763022</v>
+        <v>153.8337943169789</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>0.59456</v>
+        <v>0.6086</v>
       </c>
     </row>
     <row r="8">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>0.23044</v>
+        <v>0.23516</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>0.3878</v>
+        <v>0.39422</v>
       </c>
     </row>
     <row r="10">
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>0.14414</v>
+        <v>0.13718</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>0.21232</v>
+        <v>0.19722</v>
       </c>
     </row>
     <row r="11">
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="B11" s="21" t="n">
-        <v>0.36882</v>
+        <v>0.37194</v>
       </c>
       <c r="C11" s="21" t="n">
-        <v>0.6306</v>
+        <v>0.63126</v>
       </c>
     </row>
     <row r="12">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="B12" s="21" t="n">
-        <v>0.2549</v>
+        <v>0.24608</v>
       </c>
       <c r="C12" s="21" t="n">
-        <v>0.446</v>
+        <v>0.41858</v>
       </c>
     </row>
     <row r="14">

--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -5255,21 +5255,23 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>of which the MATURE equity premium — beta applies to this leg only</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="n">
-        <v>0.04242</v>
+          <t>Egypt country premium = sovereign default spread x 1.52</t>
+        </is>
+      </c>
+      <c r="C43" s="9">
+        <f>Assumptions!$C$31*1.52</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Egypt country premium = sovereign default spread x 1.52</t>
-        </is>
-      </c>
-      <c r="C44" s="21" t="n">
-        <v>0.05168</v>
+          <t>of which the MATURE equity premium — beta applies to this leg only</t>
+        </is>
+      </c>
+      <c r="C44" s="9">
+        <f>Assumptions!$C$32-Assumptions!$C$43</f>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -5298,28 +5300,31 @@
           <t>Country premium CHARGED — flat, once, never multiplied by beta</t>
         </is>
       </c>
-      <c r="C47" s="21" t="n">
-        <v>0.039838624</v>
+      <c r="C47" s="9">
+        <f>Assumptions!$C$45*Assumptions!$C$43+(1-Assumptions!$C$45)*Assumptions!$C$46</f>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Terminal mature equity premium</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="n">
-        <v>0.04242</v>
+          <t>Terminal Egypt country premium</t>
+        </is>
+      </c>
+      <c r="C48" s="9">
+        <f>Assumptions!$C$37-Assumptions!$C$44</f>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Terminal Egypt country premium</t>
-        </is>
-      </c>
-      <c r="C49" s="21" t="n">
-        <v>0.02758000000000001</v>
+          <t>Terminal mature equity premium</t>
+        </is>
+      </c>
+      <c r="C49" s="9">
+        <f>Assumptions!$C$37-Assumptions!$C$48</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -5328,8 +5333,9 @@
           <t>Terminal country premium CHARGED — flat and once</t>
         </is>
       </c>
-      <c r="C50" s="21" t="n">
-        <v>0.0212606279009288</v>
+      <c r="C50" s="9">
+        <f>(Assumptions!$C$45+(1-Assumptions!$C$45)*Assumptions!$C$46/Assumptions!$C$43)*Assumptions!$C$48</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -7504,7 +7510,7 @@
         </is>
       </c>
       <c r="C38" s="23">
-        <f>Assumptions!$C$43</f>
+        <f>Assumptions!$C$44</f>
         <v/>
       </c>
     </row>
@@ -7616,7 +7622,7 @@
         </is>
       </c>
       <c r="C48" s="23">
-        <f>Assumptions!$C$48</f>
+        <f>Assumptions!$C$49</f>
         <v/>
       </c>
     </row>

--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -2561,19 +2561,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>104.0301624632969</v>
+        <v>103.9579534291615</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>116.6211865067517</v>
+        <v>116.5404104409828</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>135.0183472357894</v>
+        <v>134.9250535973918</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>164.6589280440988</v>
+        <v>164.5454667217586</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>220.850419538668</v>
+        <v>220.698725084256</v>
       </c>
     </row>
     <row r="7">
@@ -2583,19 +2583,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>87.72356300452299</v>
+        <v>87.6624525757782</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>95.81640862987639</v>
+        <v>95.7497920679405</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>106.8741916763822</v>
+        <v>106.800051725385</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>123.0129544822412</v>
+        <v>122.9278341935899</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>148.9908914140809</v>
+        <v>148.8880965042395</v>
       </c>
     </row>
     <row r="8">
@@ -2605,19 +2605,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>75.41532992422788</v>
+        <v>75.36259663302229</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>80.80991954166394</v>
+        <v>80.75351613072056</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>87.82444678911774</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>97.39286004781091</v>
+        <v>97.32517470782793</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>111.3378389089451</v>
+        <v>111.2606663334557</v>
       </c>
     </row>
     <row r="9">
@@ -2627,19 +2627,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>65.80135768206051</v>
+        <v>65.7551676969633</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>69.48054631668187</v>
+        <v>69.43185339144748</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>74.08091021732177</v>
+        <v>74.02908767939394</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>80.04792691139478</v>
+        <v>79.99204503129506</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>88.16951757590688</v>
+        <v>88.10811060392669</v>
       </c>
     </row>
     <row r="10">
@@ -2649,19 +2649,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>58.08881027750758</v>
+        <v>58.047869408913</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>60.62904327864683</v>
+        <v>60.58637439004508</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>63.70252003806494</v>
+        <v>63.65776038482486</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>67.53131708874184</v>
+        <v>67.48395285635333</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>72.48070500205404</v>
+        <v>72.42997389688901</v>
       </c>
     </row>
     <row r="12">
@@ -2706,19 +2706,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>143.024503881775</v>
+        <v>142.9257201436457</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>138.9492096007453</v>
+        <v>138.8532208372788</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>135.0183472357894</v>
+        <v>134.9250535973918</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>131.2255218523266</v>
+        <v>131.1348279469485</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>127.5646799108681</v>
+        <v>127.4764945640268</v>
       </c>
     </row>
     <row r="15">
@@ -2728,19 +2728,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>113.2828955946668</v>
+        <v>113.2043612990502</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>110.0208741777526</v>
+        <v>109.9445769200784</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>106.8741916763822</v>
+        <v>106.800051725385</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>103.8377502299199</v>
+        <v>103.7656914075321</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>100.9067237627105</v>
+        <v>100.8366732530279</v>
       </c>
     </row>
     <row r="16">
@@ -2750,19 +2750,19 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>93.15227219205939</v>
+        <v>93.08744362839961</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>90.44052949139993</v>
+        <v>90.37756045690212</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>87.82444678911774</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>85.29980334431518</v>
+        <v>85.24035794052051</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>82.86260313979236</v>
+        <v>82.80482756291119</v>
       </c>
     </row>
     <row r="17">
@@ -2772,19 +2772,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>78.62924392140498</v>
+        <v>78.57430312065637</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>76.31434039371382</v>
+        <v>76.26098688087828</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>74.08091021732177</v>
+        <v>74.02908767939394</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>71.92536477488245</v>
+        <v>71.87501939979802</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>69.84430626571906</v>
+        <v>69.79538660824731</v>
       </c>
     </row>
     <row r="18">
@@ -2794,19 +2794,19 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>67.66248813099821</v>
+        <v>67.61501378418899</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>65.64711934901671</v>
+        <v>65.60102680467182</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>63.70252003806494</v>
+        <v>63.65776038482486</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>61.82557835469562</v>
+        <v>61.78210484973862</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>60.01334770570721</v>
+        <v>59.97111565861656</v>
       </c>
     </row>
     <row r="20">
@@ -2841,19 +2841,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>92.17996995001533</v>
+        <v>92.11601318377691</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>90.75790998185289</v>
+        <v>90.6948601038554</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>88.33310907770868</v>
+        <v>88.2716081141819</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>87.82381459630682</v>
+        <v>87.76263937231083</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>87.31808606401808</v>
+        <v>87.25723444154944</v>
       </c>
       <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2867,19 +2867,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>87.82444678911774</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>87.82444678911774</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>87.82444678911774</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>87.82444678911774</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>87.82444678911779</v>
+        <v>87.76327116068845</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2893,19 +2893,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>50.950588067254</v>
+        <v>50.91447338147828</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>69.38751742818589</v>
+        <v>69.33887227108335</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>87.82444678911774</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>106.2613761500496</v>
+        <v>106.1876700502934</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>124.6983055109813</v>
+        <v>124.6120689398984</v>
       </c>
       <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2919,19 +2919,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>87.82444678911776</v>
+        <v>87.76327116068842</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>87.82444678911774</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>87.82444678911774</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>87.82444678911776</v>
+        <v>87.76327116068842</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>87.82444678911777</v>
+        <v>87.76327116068845</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2945,19 +2945,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>97.59544299620889</v>
+        <v>97.52765330261191</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>92.10611928435993</v>
+        <v>92.04204535771109</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>86.98275048663422</v>
+        <v>86.92214460913688</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>81.12747186066198</v>
+        <v>81.07082946790932</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>75.63814814881297</v>
+        <v>75.58522152300843</v>
       </c>
       <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -2971,19 +2971,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>66.51825425719441</v>
+        <v>66.47156186730963</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>83.09965272761718</v>
+        <v>83.04167945779123</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>99.58803577823238</v>
+        <v>99.51884490996628</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>108.6094965282676</v>
+        <v>108.5341680585322</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>116.2624496684627</v>
+        <v>116.1819146387544</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -2997,19 +2997,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>75.41532992422788</v>
+        <v>75.36259663302229</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>80.80991954166394</v>
+        <v>80.75351613072056</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>87.82444678911774</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>97.39286004781091</v>
+        <v>97.32517470782793</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>111.3378389089451</v>
+        <v>111.2606663334557</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -4016,14 +4016,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>28.80512018233149</v>
+        <v>28.78407997537623</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>133.8678939302773</v>
+        <v>133.7753850070414</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>28.80512018233149</v>
+        <v>28.78407997537623</v>
       </c>
     </row>
     <row r="7">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>133.8678939302773</v>
+        <v>133.7753850070414</v>
       </c>
     </row>
     <row r="8">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>81.73139139510033</v>
+        <v>81.67504702609115</v>
       </c>
     </row>
     <row r="19">
@@ -4614,13 +4614,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>173.8288364577823</v>
+        <v>173.7120513766789</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>127.5665686336996</v>
+        <v>127.4805164686761</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>220.0911042818651</v>
+        <v>219.9435862846818</v>
       </c>
     </row>
     <row r="24">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>93.83596889146507</v>
+        <v>93.77232461390484</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>33.90293135551509</v>
+        <v>33.87910174981675</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>64.19639781793219</v>
+        <v>64.15244367864858</v>
       </c>
     </row>
     <row r="25">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>89.39708757884019</v>
+        <v>89.33482995346847</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>66.68784309439387</v>
+        <v>66.64132982804048</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>81.73139139510033</v>
+        <v>81.67504702609115</v>
       </c>
     </row>
     <row r="26">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>2139.355716</v>
+        <v>2140.777876</v>
       </c>
     </row>
     <row r="7">

--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -2867,19 +2867,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>84.85465173953861</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>87.7632711606884</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>93.58051000298806</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>100.8520585558626</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>87.76327116068845</v>
+        <v>108.1236071087373</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2919,19 +2919,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>87.76327116068842</v>
+        <v>83.40034202896365</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>85.58180659482602</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>87.7632711606884</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>87.76327116068842</v>
+        <v>89.94473572655079</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>87.76327116068845</v>
+        <v>92.12620029241313</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -4016,14 +4016,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>28.78407997537623</v>
+        <v>28.56127057147508</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>133.7753850070414</v>
+        <v>137.7336876137142</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>28.78407997537623</v>
+        <v>28.56127057147508</v>
       </c>
     </row>
     <row r="7">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>133.7753850070414</v>
+        <v>137.7336876137142</v>
       </c>
     </row>
     <row r="8">

--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -1176,23 +1176,23 @@
         <v>66870.86655000001</v>
       </c>
       <c r="E14" s="33">
-        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$62)</f>
+        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$66)</f>
         <v/>
       </c>
       <c r="F14" s="33">
-        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$62)</f>
+        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$66)</f>
         <v/>
       </c>
       <c r="G14" s="33">
-        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$62)</f>
+        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$66)</f>
         <v/>
       </c>
       <c r="H14" s="33">
-        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$62)</f>
+        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$66)</f>
         <v/>
       </c>
       <c r="I14" s="33">
-        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$62)</f>
+        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$66)</f>
         <v/>
       </c>
     </row>
@@ -1228,23 +1228,23 @@
         <v>55852.53459999998</v>
       </c>
       <c r="E16" s="32">
-        <f>'Income Statement'!E5*Assumptions!$C$25</f>
+        <f>'Income Statement'!E5*Assumptions!$C$29</f>
         <v/>
       </c>
       <c r="F16" s="32">
-        <f>'Income Statement'!F5*Assumptions!$C$25</f>
+        <f>'Income Statement'!F5*Assumptions!$C$29</f>
         <v/>
       </c>
       <c r="G16" s="32">
-        <f>'Income Statement'!G5*Assumptions!$C$25</f>
+        <f>'Income Statement'!G5*Assumptions!$C$29</f>
         <v/>
       </c>
       <c r="H16" s="32">
-        <f>'Income Statement'!H5*Assumptions!$C$25</f>
+        <f>'Income Statement'!H5*Assumptions!$C$29</f>
         <v/>
       </c>
       <c r="I16" s="32">
-        <f>'Income Statement'!I5*Assumptions!$C$25</f>
+        <f>'Income Statement'!I5*Assumptions!$C$29</f>
         <v/>
       </c>
     </row>
@@ -1261,27 +1261,27 @@
         <v>20902.939485</v>
       </c>
       <c r="D17" s="33">
-        <f>Assumptions!$C$54</f>
+        <f>Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="E17" s="33">
-        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$62*'Income Statement'!E17</f>
+        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$66*'Income Statement'!E17</f>
         <v/>
       </c>
       <c r="F17" s="33">
-        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$62*'Income Statement'!F17</f>
+        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$66*'Income Statement'!F17</f>
         <v/>
       </c>
       <c r="G17" s="33">
-        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$62*'Income Statement'!G17</f>
+        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$66*'Income Statement'!G17</f>
         <v/>
       </c>
       <c r="H17" s="33">
-        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$62*'Income Statement'!H17</f>
+        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$66*'Income Statement'!H17</f>
         <v/>
       </c>
       <c r="I17" s="33">
-        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$62*'Income Statement'!I17</f>
+        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$66*'Income Statement'!I17</f>
         <v/>
       </c>
     </row>
@@ -2145,27 +2145,27 @@
         </is>
       </c>
       <c r="D13" s="19">
-        <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$56</f>
+        <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="E13" s="19">
-        <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$56</f>
+        <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="F13" s="19">
-        <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$56</f>
+        <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="G13" s="19">
-        <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$56</f>
+        <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="H13" s="19">
-        <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$56</f>
+        <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="I13" s="19">
-        <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$56</f>
+        <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$60</f>
         <v/>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="C17" s="23">
-        <f>(1-Assumptions!$C$78)*(Assumptions!$C$75+Assumptions!$C$33*Assumptions!$C$76)+Assumptions!$C$78*Assumptions!$C$77*(1-Assumptions!$C$7)</f>
+        <f>(1-Assumptions!$C$82)*(Assumptions!$C$79+Assumptions!$C$37*Assumptions!$C$80)+Assumptions!$C$82*Assumptions!$C$81*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4881,776 +4881,828 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Cables — real (volume) growth over copper x FX</t>
+          <t>Cables — pass-through of copper x FX into price per tonne</t>
         </is>
       </c>
       <c r="B14" s="21" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C14" s="21" t="n">
-        <v>0.03</v>
+        <v>-0.0654</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>0.03</v>
+        <v>-0.0436</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>0.03</v>
+        <v>-0.0218</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Constructions and infrastructure — revenue growth</t>
+          <t>Cables — volume growth, the company's own disclosed tonnage</t>
         </is>
       </c>
       <c r="B15" s="21" t="n">
-        <v>0.2744</v>
+        <v>0.1071</v>
       </c>
       <c r="C15" s="21" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>0.15</v>
+        <v>0.075</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>0.115</v>
+        <v>0.065</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>0.09</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Electrical products and digital solutions — revenue growth</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="n">
-        <v>0.4828</v>
+          <t>Cables — FY2026 growth, MEASURED on the reviewed half</t>
+        </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D16" s="21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>0.11</v>
+        <v>0.3056831252933152</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Constructions — FY2026 growth, MEASURED on the reviewed half</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>0.2744315525499292</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Segment gross margins and corporate cost load</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Electrical products — FY2026 growth, MEASURED on the reviewed half</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>0.4828177529116717</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Cables — gross/segment margin</t>
+          <t>Constructions and infrastructure — revenue growth</t>
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>0.114341</v>
+        <v>0.2744</v>
       </c>
       <c r="C19" s="21" t="n">
-        <v>0.114341</v>
+        <v>0.2</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>0.114341</v>
+        <v>0.15</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>0.114341</v>
+        <v>0.115</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>0.114341</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>Electrical products and digital solutions — revenue growth</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="C20" s="21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Segment gross margins and corporate cost load</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Cables — gross/segment margin</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n">
+        <v>0.114341</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>0.114341</v>
+      </c>
+      <c r="D23" s="21" t="n">
+        <v>0.114341</v>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>0.114341</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>0.114341</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>Constructions and infrastructure — segment margin</t>
         </is>
       </c>
-      <c r="B20" s="21" t="n">
+      <c r="B24" s="21" t="n">
         <v>0.08987100000000001</v>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C24" s="21" t="n">
         <v>0.08987100000000001</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D24" s="21" t="n">
         <v>0.08987100000000001</v>
       </c>
-      <c r="E20" s="21" t="n">
+      <c r="E24" s="21" t="n">
         <v>0.08987100000000001</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="F24" s="21" t="n">
         <v>0.08987100000000001</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Electrical products and digital solutions — segment margin</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="n">
-        <v>0.236221</v>
-      </c>
-      <c r="C21" s="21" t="n">
-        <v>0.236221</v>
-      </c>
-      <c r="D21" s="21" t="n">
-        <v>0.236221</v>
-      </c>
-      <c r="E21" s="21" t="n">
-        <v>0.236221</v>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>0.236221</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Corporate cost load (% of revenue) — the bridge from segment profit to EBIT</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="n">
-        <v>0.0307</v>
-      </c>
-      <c r="C22" s="21" t="n">
-        <v>0.0307</v>
-      </c>
-      <c r="D22" s="21" t="n">
-        <v>0.0307</v>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>0.0307</v>
-      </c>
-      <c r="F22" s="21" t="n">
-        <v>0.0307</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Capital intensity</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue</t>
-        </is>
+          <t>Electrical products and digital solutions — segment margin</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>0.236221</v>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.1967</v>
+        <v>0.236221</v>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>0.236221</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>0.236221</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>0.236221</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure / revenue</t>
+          <t>Corporate cost load (% of revenue) — the bridge from segment profit to EBIT</t>
         </is>
       </c>
       <c r="B26" s="21" t="n">
-        <v>0.03574226695658529</v>
+        <v>0.0307</v>
       </c>
       <c r="C26" s="21" t="n">
-        <v>0.03574226695658529</v>
+        <v>0.0307</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>0.03574226695658529</v>
+        <v>0.0307</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>0.03574226695658529</v>
+        <v>0.0307</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>0.03574226695658529</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation and amortisation / revenue</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="n">
-        <v>0.0107</v>
-      </c>
+        <v>0.0307</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Capital intensity</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Cost of capital</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Working capital / revenue</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="n">
+        <v>0.1967</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Risk-free rate (10-year local currency)</t>
-        </is>
+          <t>Capital expenditure / revenue</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n">
+        <v>0.03574226695658529</v>
       </c>
       <c r="C30" s="21" t="n">
-        <v>0.2231</v>
+        <v>0.03574226695658529</v>
+      </c>
+      <c r="D30" s="21" t="n">
+        <v>0.03574226695658529</v>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>0.03574226695658529</v>
+      </c>
+      <c r="F30" s="21" t="n">
+        <v>0.03574226695658529</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Sovereign default spread (netted out)</t>
+          <t>Depreciation and amortisation / revenue</t>
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>0.034</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Equity risk premium, TOTAL (split into the two legs below)</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="n">
-        <v>0.0941</v>
+        <v>0.0107</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="n">
-        <v>1.224906574047969</v>
-      </c>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Cost of capital</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="13" t="n"/>
+      <c r="H33" s="13" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Cost of debt, blended</t>
+          <t>Risk-free rate (10-year local currency)</t>
         </is>
       </c>
       <c r="C34" s="21" t="n">
-        <v>0.095</v>
+        <v>0.2231</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Cost of debt path</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="n">
-        <v>0.095</v>
+          <t>Sovereign default spread (netted out)</t>
+        </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="D35" s="21" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="E35" s="21" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F35" s="21" t="n">
-        <v>0.077</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
+          <t>Equity risk premium, TOTAL (split into the two legs below)</t>
         </is>
       </c>
       <c r="C36" s="21" t="n">
-        <v>0.105</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium, TOTAL</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="n">
-        <v>0.07000000000000001</v>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="n">
+        <v>1.224906574047969</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Cost of debt, blended</t>
         </is>
       </c>
       <c r="C38" s="21" t="n">
-        <v>0.0888</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
-        </is>
+          <t>Cost of debt path</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="n">
+        <v>0.095</v>
       </c>
       <c r="C39" s="21" t="n">
-        <v>0.15</v>
+        <v>0.089</v>
+      </c>
+      <c r="D39" s="21" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F39" s="21" t="n">
+        <v>0.077</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Terminal risk-free rate</t>
         </is>
       </c>
       <c r="C40" s="21" t="n">
-        <v>0.09140000000000015</v>
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Terminal equity risk premium, TOTAL</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>The country premium, split — [R-COC-03]</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Terminal cost of debt</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n">
+        <v>0.0888</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Egypt country premium = sovereign default spread x 1.52</t>
-        </is>
-      </c>
-      <c r="C43" s="9">
-        <f>Assumptions!$C$31*1.52</f>
-        <v/>
+          <t>Terminal debt weight</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>of which the MATURE equity premium — beta applies to this leg only</t>
-        </is>
-      </c>
-      <c r="C44" s="9">
-        <f>Assumptions!$C$32-Assumptions!$C$43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Share of operations in Egypt (lambda)</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="n">
-        <v>0.5928</v>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n">
+        <v>0.09140000000000015</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Country premium on the operations outside Egypt</t>
-        </is>
-      </c>
-      <c r="C46" s="21" t="n">
-        <v>0.0226</v>
-      </c>
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>The country premium, split — [R-COC-03]</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="n"/>
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="n"/>
+      <c r="G46" s="13" t="n"/>
+      <c r="H46" s="13" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Country premium CHARGED — flat, once, never multiplied by beta</t>
+          <t>Egypt country premium = sovereign default spread x 1.52</t>
         </is>
       </c>
       <c r="C47" s="9">
-        <f>Assumptions!$C$45*Assumptions!$C$43+(1-Assumptions!$C$45)*Assumptions!$C$46</f>
+        <f>Assumptions!$C$35*1.52</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Terminal Egypt country premium</t>
+          <t>of which the MATURE equity premium — beta applies to this leg only</t>
         </is>
       </c>
       <c r="C48" s="9">
-        <f>Assumptions!$C$37-Assumptions!$C$44</f>
+        <f>Assumptions!$C$36-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Terminal mature equity premium</t>
-        </is>
-      </c>
-      <c r="C49" s="9">
-        <f>Assumptions!$C$37-Assumptions!$C$48</f>
-        <v/>
+          <t>Share of operations in Egypt (lambda)</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n">
+        <v>0.5928</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Terminal country premium CHARGED — flat and once</t>
-        </is>
-      </c>
-      <c r="C50" s="9">
-        <f>(Assumptions!$C$45+(1-Assumptions!$C$45)*Assumptions!$C$46/Assumptions!$C$43)*Assumptions!$C$48</f>
-        <v/>
+          <t>Country premium on the operations outside Egypt</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>0.0226</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Terminal beta — reverts to the market, not the measured beta</t>
-        </is>
-      </c>
-      <c r="C51" s="27" t="n">
-        <v>1</v>
+          <t>Country premium CHARGED — flat, once, never multiplied by beta</t>
+        </is>
+      </c>
+      <c r="C51" s="9">
+        <f>Assumptions!$C$49*Assumptions!$C$47+(1-Assumptions!$C$49)*Assumptions!$C$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Terminal Egypt country premium</t>
+        </is>
+      </c>
+      <c r="C52" s="9">
+        <f>Assumptions!$C$41-Assumptions!$C$48</f>
+        <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>Balance-sheet and bridge anchors</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="n"/>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
-      <c r="G53" s="13" t="n"/>
-      <c r="H53" s="13" t="n"/>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Terminal mature equity premium</t>
+        </is>
+      </c>
+      <c r="C53" s="9">
+        <f>Assumptions!$C$41-Assumptions!$C$52</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="n">
-        <v>20560.003173</v>
+          <t>Terminal country premium CHARGED — flat and once</t>
+        </is>
+      </c>
+      <c r="C54" s="9">
+        <f>(Assumptions!$C$49+(1-Assumptions!$C$49)*Assumptions!$C$50/Assumptions!$C$47)*Assumptions!$C$52</f>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Equity-accounted investees at carrying value (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C55" s="24" t="n">
-        <v>6757.650507</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Intangible assets and goodwill (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C56" s="24" t="n">
-        <v>1748.816945</v>
+          <t>Terminal beta — reverts to the market, not the measured beta</t>
+        </is>
+      </c>
+      <c r="C55" s="27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 profit after tax (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C57" s="24" t="n">
-        <v>19186.550057</v>
-      </c>
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Balance-sheet and bridge anchors</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="n"/>
+      <c r="C57" s="13" t="n"/>
+      <c r="D57" s="13" t="n"/>
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="13" t="n"/>
+      <c r="G57" s="13" t="n"/>
+      <c r="H57" s="13" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
+          <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
         </is>
       </c>
       <c r="C58" s="24" t="n">
-        <v>17330.24499</v>
+        <v>20560.003173</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>FY2024 dividend per share (EGP)</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="n">
-        <v>1</v>
+          <t>Equity-accounted investees at carrying value (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="n">
+        <v>6757.650507</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>FY2025 dividend per share (EGP, ratified 6 May 2026, paid 4 June 2026)</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>1.85</v>
+          <t>Intangible assets and goodwill (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="n">
+        <v>1748.816945</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Days the dividend compounds — 4-Jun-2026 ex-date to the 3-Sep-2026 anchor</t>
+          <t>FY2025 profit after tax (EGP mn, disclosed)</t>
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>91</v>
+        <v>19186.550057</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Forecast dividend payout ratio (struck at the actual FY2025 rate)</t>
-        </is>
-      </c>
-      <c r="C62" s="21" t="n">
-        <v>0.25</v>
+          <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="n">
+        <v>17330.24499</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Growth in the share of equity-accounted investees</t>
-        </is>
-      </c>
-      <c r="C63" s="21" t="n">
-        <v>0.08</v>
+          <t>FY2024 dividend per share (EGP) — disclosed reference, not used in the forecast</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Yield assumed on surplus cash (blend of EGP deposit and hard-currency rates)</t>
-        </is>
-      </c>
-      <c r="C64" s="21" t="n">
-        <v>0.1</v>
+          <t>FY2025 dividend per share (EGP, ratified 6 May 2026, paid 4 June 2026)</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Days from the 31-Dec-2025 valuation date to the 3-Sep-2026 anchor</t>
+          <t>Days the dividend compounds — 4-Jun-2026 ex-date to the 3-Sep-2026 anchor</t>
         </is>
       </c>
       <c r="C65" s="24" t="n">
-        <v>246</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Forecast dividend payout ratio (struck at the actual FY2025 rate)</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>Terminal construction — the sanctioned one, never g x IC</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="n"/>
-      <c r="C67" s="13" t="n"/>
-      <c r="D67" s="13" t="n"/>
-      <c r="E67" s="13" t="n"/>
-      <c r="F67" s="13" t="n"/>
-      <c r="G67" s="13" t="n"/>
-      <c r="H67" s="13" t="n"/>
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Growth in the share of equity-accounted investees</t>
+        </is>
+      </c>
+      <c r="C67" s="21" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Terminal inflation (house Egyptian macro path)</t>
+          <t>Yield assumed on surplus cash (blend of EGP deposit and hard-currency rates)</t>
         </is>
       </c>
       <c r="C68" s="21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>DISCLOSED useful life, derived by identity from note 17 (years)</t>
-        </is>
-      </c>
-      <c r="C69" s="28" t="n">
-        <v>17.2627</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>Terminal REAL growth — the stated one; nominal is derived, never supplied</t>
-        </is>
-      </c>
-      <c r="C70" s="21" t="n">
-        <v>0.02</v>
+          <t>Days from the 31-Dec-2025 valuation date to the 3-Sep-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="n">
+        <v>246</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Terminal working-capital base (EGP mn, last explicit year)</t>
-        </is>
-      </c>
-      <c r="C71" s="24" t="n">
-        <v>126491.9551090501</v>
-      </c>
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>Terminal construction — the sanctioned one, never g x IC</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="n"/>
+      <c r="C71" s="13" t="n"/>
+      <c r="D71" s="13" t="n"/>
+      <c r="E71" s="13" t="n"/>
+      <c r="F71" s="13" t="n"/>
+      <c r="G71" s="13" t="n"/>
+      <c r="H71" s="13" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Employees' statutory share of profit (mean of FY2024, FY2025, H1-2026)</t>
+          <t>Terminal inflation (house Egyptian macro path)</t>
         </is>
       </c>
       <c r="C72" s="21" t="n">
-        <v>0.1219271916645494</v>
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>DISCLOSED useful life, derived by identity from note 17 (years)</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="n">
+        <v>17.2627</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>Currency-of-discounting alternative</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="n"/>
-      <c r="C74" s="13" t="n"/>
-      <c r="D74" s="13" t="n"/>
-      <c r="E74" s="13" t="n"/>
-      <c r="F74" s="13" t="n"/>
-      <c r="G74" s="13" t="n"/>
-      <c r="H74" s="13" t="n"/>
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Terminal REAL growth — the stated one; nominal is derived, never supplied</t>
+        </is>
+      </c>
+      <c r="C74" s="21" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>US dollar risk-free rate</t>
-        </is>
-      </c>
-      <c r="C75" s="21" t="n">
-        <v>0.043</v>
+          <t>Terminal working-capital base (EGP mn, last explicit year)</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="n">
+        <v>126491.9551090501</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>Hard-currency-leg equity risk premium</t>
+          <t>Employees' statutory share of profit (mean of FY2024, FY2025, H1-2026)</t>
         </is>
       </c>
       <c r="C76" s="21" t="n">
-        <v>0.075</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>US dollar cost of debt</t>
-        </is>
-      </c>
-      <c r="C77" s="21" t="n">
-        <v>0.065</v>
+        <v>0.1219271916645494</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Debt weight, USD leg</t>
-        </is>
-      </c>
-      <c r="C78" s="21" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Currency-of-discounting alternative</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="n"/>
+      <c r="C78" s="13" t="n"/>
+      <c r="D78" s="13" t="n"/>
+      <c r="E78" s="13" t="n"/>
+      <c r="F78" s="13" t="n"/>
+      <c r="G78" s="13" t="n"/>
+      <c r="H78" s="13" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth of the USD leg</t>
+          <t>US dollar risk-free rate</t>
         </is>
       </c>
       <c r="C79" s="21" t="n">
-        <v>0.035</v>
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Hard-currency-leg equity risk premium</t>
+        </is>
+      </c>
+      <c r="C80" s="21" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="n"/>
-      <c r="C81" s="13" t="n"/>
-      <c r="D81" s="13" t="n"/>
-      <c r="E81" s="13" t="n"/>
-      <c r="F81" s="13" t="n"/>
-      <c r="G81" s="13" t="n"/>
-      <c r="H81" s="13" t="n"/>
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>US dollar cost of debt</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="n">
+        <v>0.065</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C82" s="29" t="n">
-        <v>6.5</v>
+          <t>Debt weight, USD leg</t>
+        </is>
+      </c>
+      <c r="C82" s="21" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
+          <t>Terminal growth of the USD leg — alternative currency of discounting, not used in the adopted read</t>
+        </is>
+      </c>
+      <c r="C83" s="21" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="n"/>
+      <c r="C85" s="13" t="n"/>
+      <c r="D85" s="13" t="n"/>
+      <c r="E85" s="13" t="n"/>
+      <c r="F85" s="13" t="n"/>
+      <c r="G85" s="13" t="n"/>
+      <c r="H85" s="13" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C86" s="29" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
           <t>Justified price/earnings</t>
         </is>
       </c>
-      <c r="C83" s="29" t="n">
+      <c r="C87" s="29" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C84" s="21" t="n">
+      <c r="C88" s="21" t="n">
         <v>0.235</v>
       </c>
     </row>
@@ -5755,7 +5807,7 @@
         </is>
       </c>
       <c r="C8" s="19">
-        <f>-Assumptions!$C$54</f>
+        <f>-Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="D8" s="16">
@@ -5770,7 +5822,7 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>Assumptions!$C$55</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="D9" s="16">
@@ -5857,7 +5909,7 @@
         </is>
       </c>
       <c r="C17" s="9">
-        <f>(Assumptions!$C$57-Assumptions!$C$58)/Assumptions!$C$57</f>
+        <f>(Assumptions!$C$61-Assumptions!$C$62)/Assumptions!$C$61</f>
         <v/>
       </c>
     </row>
@@ -5868,7 +5920,7 @@
         </is>
       </c>
       <c r="C18" s="17">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
     </row>
@@ -5982,20 +6034,25 @@
       <c r="D5" s="21" t="n">
         <v>0.134899552356732</v>
       </c>
-      <c r="E5" s="24" t="n">
-        <v>203416.1993989137</v>
-      </c>
-      <c r="F5" s="24" t="n">
-        <v>234967.8790996413</v>
-      </c>
-      <c r="G5" s="24" t="n">
-        <v>263666.2113229254</v>
-      </c>
-      <c r="H5" s="24" t="n">
-        <v>298687.8802405254</v>
-      </c>
-      <c r="I5" s="24" t="n">
-        <v>341526.0265398988</v>
+      <c r="E5" s="32">
+        <f>B5*(1+Assumptions!$C$16)</f>
+        <v/>
+      </c>
+      <c r="F5" s="32">
+        <f>E5*(Assumptions!$C$12*Assumptions!$C$13)/(Assumptions!$B$12*Assumptions!$B$13)*(1+Assumptions!$C$14)*(1+Assumptions!$C$15)</f>
+        <v/>
+      </c>
+      <c r="G5" s="32">
+        <f>F5*(Assumptions!$D$12*Assumptions!$D$13)/(Assumptions!$C$12*Assumptions!$C$13)*(1+Assumptions!$D$14)*(1+Assumptions!$D$15)</f>
+        <v/>
+      </c>
+      <c r="H5" s="32">
+        <f>G5*(Assumptions!$E$12*Assumptions!$E$13)/(Assumptions!$D$12*Assumptions!$D$13)*(1+Assumptions!$E$14)*(1+Assumptions!$E$15)</f>
+        <v/>
+      </c>
+      <c r="I5" s="32">
+        <f>H5*(Assumptions!$F$12*Assumptions!$F$13)/(Assumptions!$E$12*Assumptions!$E$13)*(1+Assumptions!$F$14)*(1+Assumptions!$F$15)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -6014,20 +6071,25 @@
       <c r="D6" s="21" t="n">
         <v>0.06452269254829619</v>
       </c>
-      <c r="E6" s="24" t="n">
-        <v>115920.4463847608</v>
-      </c>
-      <c r="F6" s="24" t="n">
-        <v>139104.5356617129</v>
-      </c>
-      <c r="G6" s="24" t="n">
-        <v>159970.2160109698</v>
-      </c>
-      <c r="H6" s="24" t="n">
-        <v>178366.7908522314</v>
-      </c>
-      <c r="I6" s="24" t="n">
-        <v>194419.8020289322</v>
+      <c r="E6" s="32">
+        <f>B6*(1+Assumptions!$C$17)</f>
+        <v/>
+      </c>
+      <c r="F6" s="32">
+        <f>E6*(1+Assumptions!$C$19)</f>
+        <v/>
+      </c>
+      <c r="G6" s="32">
+        <f>F6*(1+Assumptions!$D$19)</f>
+        <v/>
+      </c>
+      <c r="H6" s="32">
+        <f>G6*(1+Assumptions!$E$19)</f>
+        <v/>
+      </c>
+      <c r="I6" s="32">
+        <f>H6*(1+Assumptions!$F$19)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -6046,20 +6108,25 @@
       <c r="D7" s="21" t="n">
         <v>0.2217300370961013</v>
       </c>
-      <c r="E7" s="24" t="n">
-        <v>50857.09276164287</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <v>67639.93337298503</v>
-      </c>
-      <c r="G7" s="24" t="n">
-        <v>83197.11804877159</v>
-      </c>
-      <c r="H7" s="24" t="n">
-        <v>96508.65693657503</v>
-      </c>
-      <c r="I7" s="24" t="n">
-        <v>107124.6091995983</v>
+      <c r="E7" s="32">
+        <f>B7*(1+Assumptions!$C$18)</f>
+        <v/>
+      </c>
+      <c r="F7" s="32">
+        <f>E7*(1+Assumptions!$C$20)</f>
+        <v/>
+      </c>
+      <c r="G7" s="32">
+        <f>F7*(1+Assumptions!$D$20)</f>
+        <v/>
+      </c>
+      <c r="H7" s="32">
+        <f>G7*(1+Assumptions!$E$20)</f>
+        <v/>
+      </c>
+      <c r="I7" s="32">
+        <f>H7*(1+Assumptions!$F$20)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -6136,20 +6203,25 @@
           <t>Cables and its accessories</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
-        <v>23258.81165547119</v>
-      </c>
-      <c r="C11" s="24" t="n">
-        <v>26866.46226413209</v>
-      </c>
-      <c r="D11" s="24" t="n">
-        <v>30147.85826887461</v>
-      </c>
-      <c r="E11" s="24" t="n">
-        <v>34152.27091458192</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>39050.42740059857</v>
+      <c r="B11" s="32">
+        <f>E5*Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="C11" s="32">
+        <f>F5*Assumptions!$C$23</f>
+        <v/>
+      </c>
+      <c r="D11" s="32">
+        <f>G5*Assumptions!$D$23</f>
+        <v/>
+      </c>
+      <c r="E11" s="32">
+        <f>H5*Assumptions!$E$23</f>
+        <v/>
+      </c>
+      <c r="F11" s="32">
+        <f>I5*Assumptions!$F$23</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -6158,20 +6230,25 @@
           <t>Constructions and infrastructure</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
-        <v>10417.88643704483</v>
-      </c>
-      <c r="C12" s="24" t="n">
-        <v>12501.4637244538</v>
-      </c>
-      <c r="D12" s="24" t="n">
-        <v>14376.68328312187</v>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>16030.00186068088</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <v>17472.70202814217</v>
+      <c r="B12" s="32">
+        <f>E6*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="C12" s="32">
+        <f>F6*Assumptions!$C$24</f>
+        <v/>
+      </c>
+      <c r="D12" s="32">
+        <f>G6*Assumptions!$D$24</f>
+        <v/>
+      </c>
+      <c r="E12" s="32">
+        <f>H6*Assumptions!$E$24</f>
+        <v/>
+      </c>
+      <c r="F12" s="32">
+        <f>I6*Assumptions!$F$24</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -6180,20 +6257,25 @@
           <t>Electrical products and digital solutions</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
-        <v>12013.51330924804</v>
-      </c>
-      <c r="C13" s="24" t="n">
-        <v>15977.9727012999</v>
-      </c>
-      <c r="D13" s="24" t="n">
-        <v>19652.90642259887</v>
-      </c>
-      <c r="E13" s="24" t="n">
-        <v>22797.37145021469</v>
-      </c>
-      <c r="F13" s="24" t="n">
-        <v>25305.08230973831</v>
+      <c r="B13" s="32">
+        <f>E7*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="C13" s="32">
+        <f>F7*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="D13" s="32">
+        <f>G7*Assumptions!$D$25</f>
+        <v/>
+      </c>
+      <c r="E13" s="32">
+        <f>H7*Assumptions!$E$25</f>
+        <v/>
+      </c>
+      <c r="F13" s="32">
+        <f>I7*Assumptions!$F$25</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -6289,23 +6371,23 @@
         </is>
       </c>
       <c r="B18" s="32">
-        <f>B11-Assumptions!$B$22*E5</f>
+        <f>B11-Assumptions!$B$26*E5</f>
         <v/>
       </c>
       <c r="C18" s="32">
-        <f>C11-Assumptions!$C$22*F5</f>
+        <f>C11-Assumptions!$C$26*F5</f>
         <v/>
       </c>
       <c r="D18" s="32">
-        <f>D11-Assumptions!$D$22*G5</f>
+        <f>D11-Assumptions!$D$26*G5</f>
         <v/>
       </c>
       <c r="E18" s="32">
-        <f>E11-Assumptions!$E$22*H5</f>
+        <f>E11-Assumptions!$E$26*H5</f>
         <v/>
       </c>
       <c r="F18" s="32">
-        <f>F11-Assumptions!$F$22*I5</f>
+        <f>F11-Assumptions!$F$26*I5</f>
         <v/>
       </c>
     </row>
@@ -6316,23 +6398,23 @@
         </is>
       </c>
       <c r="B19" s="32">
-        <f>B12-Assumptions!$B$22*E6</f>
+        <f>B12-Assumptions!$B$26*E6</f>
         <v/>
       </c>
       <c r="C19" s="32">
-        <f>C12-Assumptions!$C$22*F6</f>
+        <f>C12-Assumptions!$C$26*F6</f>
         <v/>
       </c>
       <c r="D19" s="32">
-        <f>D12-Assumptions!$D$22*G6</f>
+        <f>D12-Assumptions!$D$26*G6</f>
         <v/>
       </c>
       <c r="E19" s="32">
-        <f>E12-Assumptions!$E$22*H6</f>
+        <f>E12-Assumptions!$E$26*H6</f>
         <v/>
       </c>
       <c r="F19" s="32">
-        <f>F12-Assumptions!$F$22*I6</f>
+        <f>F12-Assumptions!$F$26*I6</f>
         <v/>
       </c>
     </row>
@@ -6343,23 +6425,23 @@
         </is>
       </c>
       <c r="B20" s="32">
-        <f>B13-Assumptions!$B$22*E7</f>
+        <f>B13-Assumptions!$B$26*E7</f>
         <v/>
       </c>
       <c r="C20" s="32">
-        <f>C13-Assumptions!$C$22*F7</f>
+        <f>C13-Assumptions!$C$26*F7</f>
         <v/>
       </c>
       <c r="D20" s="32">
-        <f>D13-Assumptions!$D$22*G7</f>
+        <f>D13-Assumptions!$D$26*G7</f>
         <v/>
       </c>
       <c r="E20" s="32">
-        <f>E13-Assumptions!$E$22*H7</f>
+        <f>E13-Assumptions!$E$26*H7</f>
         <v/>
       </c>
       <c r="F20" s="32">
-        <f>F13-Assumptions!$F$22*I7</f>
+        <f>F13-Assumptions!$F$26*I7</f>
         <v/>
       </c>
     </row>
@@ -6397,23 +6479,23 @@
         </is>
       </c>
       <c r="B22" s="32">
-        <f>Assumptions!$C$27*E8</f>
+        <f>Assumptions!$C$31*E8</f>
         <v/>
       </c>
       <c r="C22" s="32">
-        <f>Assumptions!$C$27*F8</f>
+        <f>Assumptions!$C$31*F8</f>
         <v/>
       </c>
       <c r="D22" s="32">
-        <f>Assumptions!$C$27*G8</f>
+        <f>Assumptions!$C$31*G8</f>
         <v/>
       </c>
       <c r="E22" s="32">
-        <f>Assumptions!$C$27*H8</f>
+        <f>Assumptions!$C$31*H8</f>
         <v/>
       </c>
       <c r="F22" s="32">
-        <f>Assumptions!$C$27*I8</f>
+        <f>Assumptions!$C$31*I8</f>
         <v/>
       </c>
     </row>
@@ -6540,7 +6622,7 @@
         </is>
       </c>
       <c r="C6" s="36">
-        <f>Assumptions!$C$82</f>
+        <f>Assumptions!$C$86</f>
         <v/>
       </c>
     </row>
@@ -6596,7 +6678,7 @@
       </c>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="34">
-        <f>((C10-Assumptions!$C$54+Assumptions!$C$55)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
+        <f>((C10-Assumptions!$C$58+Assumptions!$C$59)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$64*(1+DCF!$C$39)^(Assumptions!$C$65/365)</f>
         <v/>
       </c>
     </row>
@@ -6607,11 +6689,11 @@
         </is>
       </c>
       <c r="C12" s="16">
-        <f>((5.5*C5*C8+C9-Assumptions!$C$54+Assumptions!$C$55)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
+        <f>((5.5*C5*C8+C9-Assumptions!$C$58+Assumptions!$C$59)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$64*(1+DCF!$C$39)^(Assumptions!$C$65/365)</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>((8.0*C5*C8+C9-Assumptions!$C$54+Assumptions!$C$55)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
+        <f>((8.0*C5*C8+C9-Assumptions!$C$58+Assumptions!$C$59)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$64*(1+DCF!$C$39)^(Assumptions!$C$65/365)</f>
         <v/>
       </c>
     </row>
@@ -6622,7 +6704,7 @@
         </is>
       </c>
       <c r="C13" s="38">
-        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$54)/'Income Statement'!D7</f>
+        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$58)/'Income Statement'!D7</f>
         <v/>
       </c>
     </row>
@@ -6655,7 +6737,7 @@
         </is>
       </c>
       <c r="C16" s="38">
-        <f>Assumptions!$C$54/'Income Statement'!D7</f>
+        <f>Assumptions!$C$58/'Income Statement'!D7</f>
         <v/>
       </c>
     </row>
@@ -6711,7 +6793,7 @@
         </is>
       </c>
       <c r="C22" s="32">
-        <f>C21-C19*Assumptions!$C$27</f>
+        <f>C21-C19*Assumptions!$C$31</f>
         <v/>
       </c>
     </row>
@@ -6766,7 +6848,7 @@
         </is>
       </c>
       <c r="C27" s="38">
-        <f>Assumptions!$C$83</f>
+        <f>Assumptions!$C$87</f>
         <v/>
       </c>
     </row>
@@ -6778,7 +6860,7 @@
       </c>
       <c r="B28" s="13" t="n"/>
       <c r="C28" s="34">
-        <f>C26*C27*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
+        <f>C26*C27*DCF!$C$61-Assumptions!$C$64*(1+DCF!$C$39)^(Assumptions!$C$65/365)</f>
         <v/>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -6787,11 +6869,11 @@
         </is>
       </c>
       <c r="E28" s="16">
-        <f>C26*7*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
+        <f>C26*7*DCF!$C$61-Assumptions!$C$64*(1+DCF!$C$39)^(Assumptions!$C$65/365)</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>C26*11.5*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
+        <f>C26*11.5*DCF!$C$61-Assumptions!$C$64*(1+DCF!$C$39)^(Assumptions!$C$65/365)</f>
         <v/>
       </c>
     </row>
@@ -6825,7 +6907,7 @@
         </is>
       </c>
       <c r="C32" s="9">
-        <f>Assumptions!$C$84</f>
+        <f>Assumptions!$C$88</f>
         <v/>
       </c>
     </row>
@@ -6858,7 +6940,7 @@
         </is>
       </c>
       <c r="C35" s="38">
-        <f>(C32-Assumptions!$C$40)/(C34-Assumptions!$C$40)</f>
+        <f>(C32-Assumptions!$C$44)/(C34-Assumptions!$C$44)</f>
         <v/>
       </c>
     </row>
@@ -6870,7 +6952,7 @@
       </c>
       <c r="B36" s="13" t="n"/>
       <c r="C36" s="34">
-        <f>C31*C35*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
+        <f>C31*C35*DCF!$C$61-Assumptions!$C$64*(1+DCF!$C$39)^(Assumptions!$C$65/365)</f>
         <v/>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -6879,11 +6961,11 @@
         </is>
       </c>
       <c r="E36" s="16">
-        <f>((Assumptions!$C$84-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
+        <f>((Assumptions!$C$88-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$64*(1+DCF!$C$39)^(Assumptions!$C$65/365)</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>((Assumptions!$C$84+0.02-Assumptions!$C$40)/(DCF!C49-Assumptions!$C$40))*C31*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
+        <f>((Assumptions!$C$88+0.02-Assumptions!$C$44)/(DCF!C49-Assumptions!$C$44))*C31*DCF!$C$61-Assumptions!$C$64*(1+DCF!$C$39)^(Assumptions!$C$65/365)</f>
         <v/>
       </c>
     </row>
@@ -7048,23 +7130,23 @@
         </is>
       </c>
       <c r="B8" s="32">
-        <f>-B5*Assumptions!$C$27</f>
+        <f>-B5*Assumptions!$C$31</f>
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>-C5*Assumptions!$C$27</f>
+        <f>-C5*Assumptions!$C$31</f>
         <v/>
       </c>
       <c r="D8" s="32">
-        <f>-D5*Assumptions!$C$27</f>
+        <f>-D5*Assumptions!$C$31</f>
         <v/>
       </c>
       <c r="E8" s="32">
-        <f>-E5*Assumptions!$C$27</f>
+        <f>-E5*Assumptions!$C$31</f>
         <v/>
       </c>
       <c r="F8" s="32">
-        <f>-F5*Assumptions!$C$27</f>
+        <f>-F5*Assumptions!$C$31</f>
         <v/>
       </c>
     </row>
@@ -7156,23 +7238,23 @@
         </is>
       </c>
       <c r="B12" s="32">
-        <f>-B5*Assumptions!$B$26</f>
+        <f>-B5*Assumptions!$B$30</f>
         <v/>
       </c>
       <c r="C12" s="32">
-        <f>-C5*Assumptions!$C$26</f>
+        <f>-C5*Assumptions!$C$30</f>
         <v/>
       </c>
       <c r="D12" s="32">
-        <f>-D5*Assumptions!$D$26</f>
+        <f>-D5*Assumptions!$D$30</f>
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>-E5*Assumptions!$E$26</f>
+        <f>-E5*Assumptions!$E$30</f>
         <v/>
       </c>
       <c r="F12" s="32">
-        <f>-F5*Assumptions!$F$26</f>
+        <f>-F5*Assumptions!$F$30</f>
         <v/>
       </c>
     </row>
@@ -7183,23 +7265,23 @@
         </is>
       </c>
       <c r="B13" s="32">
-        <f>-(B5*Assumptions!$C$25-'Balance Sheet'!D16)</f>
+        <f>-(B5*Assumptions!$C$29-'Balance Sheet'!D16)</f>
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>-(C5-B5)*Assumptions!$C$25</f>
+        <f>-(C5-B5)*Assumptions!$C$29</f>
         <v/>
       </c>
       <c r="D13" s="32">
-        <f>-(D5-C5)*Assumptions!$C$25</f>
+        <f>-(D5-C5)*Assumptions!$C$29</f>
         <v/>
       </c>
       <c r="E13" s="32">
-        <f>-(E5-D5)*Assumptions!$C$25</f>
+        <f>-(E5-D5)*Assumptions!$C$29</f>
         <v/>
       </c>
       <c r="F13" s="32">
-        <f>-(F5-E5)*Assumptions!$C$25</f>
+        <f>-(F5-E5)*Assumptions!$C$29</f>
         <v/>
       </c>
     </row>
@@ -7358,7 +7440,7 @@
         </is>
       </c>
       <c r="C23" s="17">
-        <f>Assumptions!$C$40</f>
+        <f>Assumptions!$C$44</f>
         <v/>
       </c>
     </row>
@@ -7466,7 +7548,7 @@
         </is>
       </c>
       <c r="C34" s="23">
-        <f>Assumptions!$C$30</f>
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
     </row>
@@ -7477,7 +7559,7 @@
         </is>
       </c>
       <c r="C35" s="23">
-        <f>Assumptions!$C$31</f>
+        <f>Assumptions!$C$35</f>
         <v/>
       </c>
     </row>
@@ -7499,7 +7581,7 @@
         </is>
       </c>
       <c r="C37" s="41">
-        <f>Assumptions!$C$33</f>
+        <f>Assumptions!$C$37</f>
         <v/>
       </c>
     </row>
@@ -7510,7 +7592,7 @@
         </is>
       </c>
       <c r="C38" s="23">
-        <f>Assumptions!$C$44</f>
+        <f>Assumptions!$C$48</f>
         <v/>
       </c>
     </row>
@@ -7521,7 +7603,7 @@
         </is>
       </c>
       <c r="C39" s="39">
-        <f>C36+C37*C38+Assumptions!$C$47</f>
+        <f>C36+C37*C38+Assumptions!$C$51</f>
         <v/>
       </c>
     </row>
@@ -7532,7 +7614,7 @@
         </is>
       </c>
       <c r="C40" s="23">
-        <f>Assumptions!$C$34</f>
+        <f>Assumptions!$C$38</f>
         <v/>
       </c>
     </row>
@@ -7565,7 +7647,7 @@
         </is>
       </c>
       <c r="C43" s="19">
-        <f>Assumptions!$C$54</f>
+        <f>Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -7611,7 +7693,7 @@
         </is>
       </c>
       <c r="C47" s="23">
-        <f>Assumptions!$C$36</f>
+        <f>Assumptions!$C$40</f>
         <v/>
       </c>
     </row>
@@ -7622,7 +7704,7 @@
         </is>
       </c>
       <c r="C48" s="23">
-        <f>Assumptions!$C$49</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -7633,7 +7715,7 @@
         </is>
       </c>
       <c r="C49" s="39">
-        <f>C47+Assumptions!$C$51*C48+Assumptions!$C$50</f>
+        <f>C47+Assumptions!$C$55*C48+Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -7644,7 +7726,7 @@
         </is>
       </c>
       <c r="C50" s="23">
-        <f>Assumptions!$C$38</f>
+        <f>Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
@@ -7666,7 +7748,7 @@
         </is>
       </c>
       <c r="C52" s="23">
-        <f>Assumptions!$C$39</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
@@ -7722,23 +7804,23 @@
         </is>
       </c>
       <c r="B56" s="23">
-        <f>Assumptions!$B$35</f>
+        <f>Assumptions!$B$39</f>
         <v/>
       </c>
       <c r="C56" s="23">
-        <f>Assumptions!$C$35</f>
+        <f>Assumptions!$C$39</f>
         <v/>
       </c>
       <c r="D56" s="23">
-        <f>Assumptions!$D$35</f>
+        <f>Assumptions!$D$39</f>
         <v/>
       </c>
       <c r="E56" s="23">
-        <f>Assumptions!$E$35</f>
+        <f>Assumptions!$E$39</f>
         <v/>
       </c>
       <c r="F56" s="23">
-        <f>Assumptions!$F$35</f>
+        <f>Assumptions!$F$39</f>
         <v/>
       </c>
     </row>
@@ -7790,7 +7872,7 @@
         </is>
       </c>
       <c r="C61" s="40">
-        <f>(1+C39)^(Assumptions!$C$65/365)</f>
+        <f>(1+C39)^(Assumptions!$C$69/365)</f>
         <v/>
       </c>
     </row>
@@ -7802,7 +7884,7 @@
       </c>
       <c r="B62" s="13" t="n"/>
       <c r="C62" s="34">
-        <f>C31*C61-Assumptions!$C$60*(1+$C$39)^(Assumptions!$C$61/365)</f>
+        <f>C31*C61-Assumptions!$C$64*(1+$C$39)^(Assumptions!$C$65/365)</f>
         <v/>
       </c>
       <c r="D62" s="13" t="n"/>
@@ -7828,7 +7910,7 @@
         </is>
       </c>
       <c r="C65" s="19">
-        <f>F8*(1+Assumptions!$C$68)^(Assumptions!$C$69/2)</f>
+        <f>F8*(1+Assumptions!$C$72)^(Assumptions!$C$73/2)</f>
         <v/>
       </c>
     </row>
@@ -7839,7 +7921,7 @@
         </is>
       </c>
       <c r="C66" s="19">
-        <f>-Assumptions!$C$70*'Summary Financials'!I13</f>
+        <f>-Assumptions!$C$74*'Summary Financials'!I13</f>
         <v/>
       </c>
     </row>
@@ -7850,7 +7932,7 @@
         </is>
       </c>
       <c r="C67" s="19">
-        <f>-Assumptions!$C$71*Assumptions!$C$68</f>
+        <f>-Assumptions!$C$75*Assumptions!$C$72</f>
         <v/>
       </c>
     </row>
@@ -8197,23 +8279,23 @@
         <v>-2145.438755</v>
       </c>
       <c r="E11" s="32">
-        <f>-(Assumptions!$B$35*'Balance Sheet'!$D$11-Assumptions!$C$64*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
+        <f>-(Assumptions!$B$39*'Balance Sheet'!$D$11-Assumptions!$C$68*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
         <v/>
       </c>
       <c r="F11" s="32">
-        <f>-(Assumptions!$C$35*'Balance Sheet'!$D$11-Assumptions!$C$64*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
+        <f>-(Assumptions!$C$39*'Balance Sheet'!$D$11-Assumptions!$C$68*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
         <v/>
       </c>
       <c r="G11" s="32">
-        <f>-(Assumptions!$D$35*'Balance Sheet'!$D$11-Assumptions!$C$64*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
+        <f>-(Assumptions!$D$39*'Balance Sheet'!$D$11-Assumptions!$C$68*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
         <v/>
       </c>
       <c r="H11" s="32">
-        <f>-(Assumptions!$E$35*'Balance Sheet'!$D$11-Assumptions!$C$64*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
+        <f>-(Assumptions!$E$39*'Balance Sheet'!$D$11-Assumptions!$C$68*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
         <v/>
       </c>
       <c r="I11" s="32">
-        <f>-(Assumptions!$F$35*'Balance Sheet'!$D$11-Assumptions!$C$64*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
+        <f>-(Assumptions!$F$39*'Balance Sheet'!$D$11-Assumptions!$C$68*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
         <v/>
       </c>
     </row>
@@ -8233,23 +8315,23 @@
         <v>1568.902975</v>
       </c>
       <c r="E12" s="32">
-        <f>D12*(1+Assumptions!$C$63)</f>
+        <f>D12*(1+Assumptions!$C$67)</f>
         <v/>
       </c>
       <c r="F12" s="32">
-        <f>E12*(1+Assumptions!$C$63)</f>
+        <f>E12*(1+Assumptions!$C$67)</f>
         <v/>
       </c>
       <c r="G12" s="32">
-        <f>F12*(1+Assumptions!$C$63)</f>
+        <f>F12*(1+Assumptions!$C$67)</f>
         <v/>
       </c>
       <c r="H12" s="32">
-        <f>G12*(1+Assumptions!$C$63)</f>
+        <f>G12*(1+Assumptions!$C$67)</f>
         <v/>
       </c>
       <c r="I12" s="32">
-        <f>H12*(1+Assumptions!$C$63)</f>
+        <f>H12*(1+Assumptions!$C$67)</f>
         <v/>
       </c>
     </row>

--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -2303,51 +2303,51 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>One month — to 2026-09-06</t>
+          <t>One month — to 2026-10-04</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>87.56537469454608</v>
+        <v>109.5074167265576</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>99.48409928257496</v>
+        <v>124.0514957843762</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>106.9944391060197</v>
+        <v>133.0616563686112</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>115.0917272987826</v>
+        <v>142.7314893420786</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>131.1946500992745</v>
+        <v>161.6387745143835</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>0.56294</v>
+        <v>0.5907</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Three months — to 2026-11-05</t>
+          <t>Three months — to 2026-12-03</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>79.1329359945467</v>
+        <v>98.48901557567697</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>97.94831820710576</v>
+        <v>122.2212388578727</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>110.42539731263</v>
+        <v>137.99004315834</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>124.4873816166916</v>
+        <v>155.78764256831</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>153.8337943169789</v>
+        <v>193.0056349056027</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>0.6086</v>
+        <v>0.6309</v>
       </c>
     </row>
     <row r="8">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>0.23516</v>
+        <v>0.24454</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>0.39422</v>
+        <v>0.41946</v>
       </c>
     </row>
     <row r="10">
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>0.13718</v>
+        <v>0.11996</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>0.19722</v>
+        <v>0.18412</v>
       </c>
     </row>
     <row r="11">
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="B11" s="21" t="n">
-        <v>0.37194</v>
+        <v>0.37802</v>
       </c>
       <c r="C11" s="21" t="n">
-        <v>0.63126</v>
+        <v>0.65432</v>
       </c>
     </row>
     <row r="12">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="B12" s="21" t="n">
-        <v>0.24608</v>
+        <v>0.22024</v>
       </c>
       <c r="C12" s="21" t="n">
-        <v>0.41858</v>
+        <v>0.40498</v>
       </c>
     </row>
     <row r="14">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>0.4838094309558744</v>
+        <v>0.4932051127914256</v>
       </c>
     </row>
     <row r="17">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>

--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -4638,10 +4638,10 @@
         <v>93.77232461390484</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>33.87910174981675</v>
+        <v>66.99952105349392</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>64.15244367864858</v>
+        <v>154.5203160036869</v>
       </c>
     </row>
     <row r="25">
@@ -4662,7 +4662,7 @@
         <v>66.64132982804048</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>81.67504702609115</v>
+        <v>112.0283300788964</v>
       </c>
     </row>
     <row r="26">

--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -709,188 +709,202 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>driver — Cables on copper-price growth times FX-translation growth times a modest real-volume assumption,</t>
+          <t>driver — Cables on DISCLOSED TONNAGE (185,449 tonnes in FY2025, from the company's own quarterly</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Constructions and Electrical products on a taper of their own recent revenue CAGR — because none of the</t>
+          <t>releases) times a copper and currency pass-through measured out of the segment's own audited revenue</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>audited filings discloses a tonnage, order-book or backlog figure to build a literal unit model from.</t>
+          <t>per tonne; Constructions and Electrical products on a taper of their own recent revenue CAGR. The</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Margins come from the same segment build; group EBITDA margin is an OUTPUT of it, not an input.</t>
+          <t>AUDITED filings disclose no tonnage, order-book or backlog figure for any segment — the releases do,</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>they are the issuer's own, and they are not audited, which is why they drive a volume and not a value.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>Margins come from the same segment build; group EBITDA margin is an OUTPUT of it, not an input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>shown as ranges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
+          <t>shown as ranges.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>financial statements — every income-statement, balance-sheet and segment line is the audited figure, not a</t>
-        </is>
-      </c>
+      <c r="A35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>derivation or a triangulation. Segment revenue ties EXACTLY to consolidated revenue in every year (Note</t>
+          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5-3); segment profit reconciles to consolidated operating profit through an explicit, exactly-reconciling</t>
+          <t>financial statements — every income-statement, balance-sheet and segment line is the audited figure, not a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>corporate cost load (Note 16 less G&amp;A, net impairment, other expenses and other income). Every input is</t>
+          <t>derivation or a triangulation. Segment revenue ties EXACTLY to consolidated revenue in every year (Note</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>annotated where it appears and listed with source and date in the companion bibliography document.</t>
+          <t>5-3); segment profit reconciles to consolidated operating profit through an explicit, exactly-reconciling</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr"/>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>corporate cost load (Note 16 less G&amp;A, net impairment, other expenses and other income). Every input is</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
+          <t>annotated where it appears and listed with source and date in the companion bibliography document.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>26.7% -&gt; 15.3% on the same easing calendar as the interest forecast; the terminal value is</t>
-        </is>
-      </c>
+      <c r="A42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
+          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>The glide fractions are not a free parameter: they are the cost-of-debt path's own cumulative progress, and</t>
+          <t>26.7% -&gt; 15.3% on the same easing calendar as the interest forecast; the terminal value is</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>the DCF sheet computes them in front of you.</t>
+          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr"/>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>The glide fractions are not a free parameter: they are the cost-of-debt path's own cumulative progress, and</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>The open question. This company earns just over half its revenue on a hard-currency-linked basis but</t>
+          <t>the DCF sheet computes them in front of you.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>reports, lists and borrows in Egyptian pounds. The primary model charges the full Egyptian cost of capital.</t>
-        </is>
-      </c>
+      <c r="A48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>The Fundamental Valuation sheet also shows what the same cash flows are worth if the hard-currency leg is</t>
+          <t>The open question. This company earns just over half its revenue on a hard-currency-linked basis but</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>discounted at a hard-currency rate. Both are shown; they are not averaged.</t>
+          <t>reports, lists and borrows in Egyptian pounds. The primary model charges the full Egyptian cost of capital.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr"/>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>The Fundamental Valuation sheet also shows what the same cash flows are worth if the hard-currency leg is</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Currency. EGP million unless stated. Spot EGP 130.00 (2026-09-03 close). Sheets: READ FIRST · Summary ·</t>
+          <t>discounted at a hard-currency rate. Both are shown; they are not averaged.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
-        </is>
-      </c>
+      <c r="A53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+          <t>Currency. EGP million unless stated. Spot EGP 130.00 (2026-09-03 close). Sheets: READ FIRST · Summary ·</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>

--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -2575,19 +2575,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>103.9579534291615</v>
+        <v>104.2101859237371</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>116.5404104409828</v>
+        <v>116.8098706699302</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>134.9250535973918</v>
+        <v>135.219146258418</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>164.5454667217586</v>
+        <v>164.8785308033142</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>220.698725084256</v>
+        <v>221.1046215644958</v>
       </c>
     </row>
     <row r="7">
@@ -2597,19 +2597,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>87.6624525757782</v>
+        <v>87.86914264056945</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>95.7497920679405</v>
+        <v>95.96502215447296</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>106.800051725385</v>
+        <v>107.0264794129917</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>122.9278341935899</v>
+        <v>123.1700137459473</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>148.8880965042395</v>
+        <v>149.1548471246215</v>
       </c>
     </row>
     <row r="8">
@@ -2619,19 +2619,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>75.36259663302229</v>
+        <v>75.53391452021511</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>80.75351613072056</v>
+        <v>80.92847382063268</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.94253027526975</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>97.32517470782793</v>
+        <v>97.50977831627539</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>111.2606663334557</v>
+        <v>111.452401931667</v>
       </c>
     </row>
     <row r="9">
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>65.7551676969633</v>
+        <v>65.89800648265457</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>69.43185339144748</v>
+        <v>69.57543582124129</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>74.02908767939394</v>
+        <v>74.17318967641987</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>79.99204503129506</v>
+        <v>80.1363341557968</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>88.10811060392669</v>
+        <v>88.25206275347753</v>
       </c>
     </row>
     <row r="10">
@@ -2663,19 +2663,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>58.047869408913</v>
+        <v>58.16712816218472</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>60.58637439004508</v>
+        <v>60.7046157451272</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>63.65776038482486</v>
+        <v>63.77436696970145</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>67.48395285635333</v>
+        <v>67.59805018613132</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>72.42997389688901</v>
+        <v>72.5402645884689</v>
       </c>
     </row>
     <row r="12">
@@ -2720,19 +2720,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>142.9257201436457</v>
+        <v>143.241161592152</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>138.8532208372788</v>
+        <v>139.1577769068532</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>134.9250535973918</v>
+        <v>135.219146258418</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>131.1348279469485</v>
+        <v>131.4188596590871</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>127.4764945640268</v>
+        <v>127.7508493430342</v>
       </c>
     </row>
     <row r="15">
@@ -2742,19 +2742,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>113.2043612990502</v>
+        <v>113.4482630797391</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>109.9445769200784</v>
+        <v>110.179566181293</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>106.800051725385</v>
+        <v>107.0264794129917</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>103.7656914075321</v>
+        <v>103.9838921385165</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>100.8366732530279</v>
+        <v>101.0469662109245</v>
       </c>
     </row>
     <row r="16">
@@ -2764,19 +2764,19 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>93.08744362839961</v>
+        <v>93.28146797926233</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>90.37756045690212</v>
+        <v>90.56405159320151</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.94253027526975</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>85.24035794052051</v>
+        <v>85.41267212934591</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>82.80482756291119</v>
+        <v>82.97047060014312</v>
       </c>
     </row>
     <row r="17">
@@ -2786,19 +2786,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>78.57430312065637</v>
+        <v>78.73114527643777</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>76.26098688087828</v>
+        <v>76.41132699503298</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>74.02908767939394</v>
+        <v>74.17318967641987</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>71.87501939979802</v>
+        <v>72.01313478150634</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>69.79538660824731</v>
+        <v>69.92775513848943</v>
       </c>
     </row>
     <row r="18">
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>67.61501378418899</v>
+        <v>67.74277207327435</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>65.60102680467182</v>
+        <v>65.72309192406004</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>63.65776038482486</v>
+        <v>63.77436696970145</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>61.78210484973862</v>
+        <v>61.8934764300487</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>59.97111565861656</v>
+        <v>60.07746527262637</v>
       </c>
     </row>
     <row r="20">
@@ -2855,19 +2855,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>92.11601318377691</v>
+        <v>92.3073328407132</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>90.6948601038554</v>
+        <v>90.88223139673786</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>88.2716081141819</v>
+        <v>88.4522706716469</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>87.76263937231083</v>
+        <v>87.94189674346777</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>87.25723444154944</v>
+        <v>87.43509782336898</v>
       </c>
       <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2881,19 +2881,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>84.85465173953861</v>
+        <v>85.01598494266179</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.94253027526975</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>93.58051000298806</v>
+        <v>93.79562094048565</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>100.8520585558626</v>
+        <v>101.1119842720056</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>108.1236071087373</v>
+        <v>108.4283476035255</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>50.91447338147828</v>
+        <v>50.94299420291501</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>69.33887227108335</v>
+        <v>69.44276223909237</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.94253027526975</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>106.1876700502934</v>
+        <v>106.442298311447</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>124.6120689398984</v>
+        <v>124.9420663476243</v>
       </c>
       <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2933,19 +2933,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>83.40034202896365</v>
+        <v>83.55271227635778</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>85.58180659482602</v>
+        <v>85.74762127581378</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.94253027526975</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>89.94473572655079</v>
+        <v>90.13743927472571</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>92.12620029241313</v>
+        <v>92.33234827418168</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2959,19 +2959,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>97.52765330261191</v>
+        <v>97.75178736220548</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>92.04204535771109</v>
+        <v>92.24096877403932</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>86.92214460913688</v>
+        <v>87.09753809175092</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>81.07082946790932</v>
+        <v>81.21933159770705</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>75.58522152300843</v>
+        <v>75.70851300954091</v>
       </c>
       <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -2981,23 +2981,23 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital  (15.0% / 18.0% / 22.5% / 26.0% / 30.0%)</t>
+          <t>Terminal return on invested capital  (15.0% / 18.0% / 22.4% / 26.0% / 30.0%)</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>66.47156186730963</v>
+        <v>66.63013824272224</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>83.04167945779123</v>
+        <v>83.24518221853894</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>99.51884490996628</v>
+        <v>99.66193933569537</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>108.5341680585322</v>
+        <v>108.80678833518</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>116.1819146387544</v>
+        <v>116.4752701701724</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -3011,19 +3011,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>75.36259663302229</v>
+        <v>75.53391452021511</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>80.75351613072056</v>
+        <v>80.92847382063268</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.94253027526975</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>97.32517470782793</v>
+        <v>97.50977831627539</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>111.2606663334557</v>
+        <v>111.452401931667</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -4030,14 +4030,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>28.56127057147508</v>
+        <v>28.56691644232448</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>137.7336876137142</v>
+        <v>138.175135007335</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>28.56127057147508</v>
+        <v>28.56691644232448</v>
       </c>
     </row>
     <row r="7">
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>137.7336876137142</v>
+        <v>138.175135007335</v>
       </c>
     </row>
     <row r="8">
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>0.5108677256872055</v>
+        <v>0.5113017981964768</v>
       </c>
     </row>
     <row r="16">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>81.67504702609115</v>
+        <v>79.09245631047411</v>
       </c>
     </row>
     <row r="19">
@@ -4628,13 +4628,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>173.7120513766789</v>
+        <v>176.1268087989355</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>127.4805164686761</v>
+        <v>129.2598114113915</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>219.9435862846818</v>
+        <v>222.9938061864796</v>
       </c>
     </row>
     <row r="24">
@@ -4649,13 +4649,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>93.77232461390484</v>
+        <v>97.71822108324348</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>66.99952105349392</v>
+        <v>69.84198537113525</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>154.5203160036869</v>
+        <v>160.9699206371431</v>
       </c>
     </row>
     <row r="25">
@@ -4670,13 +4670,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>89.33482995346847</v>
+        <v>89.4341891885301</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>66.64132982804048</v>
+        <v>66.70493817011291</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>112.0283300788964</v>
+        <v>112.1634402069473</v>
       </c>
     </row>
     <row r="26">
@@ -4877,19 +4877,19 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>51</v>
+        <v>53.9711</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>54</v>
+        <v>58.9733</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>57.5</v>
+        <v>62.7131</v>
       </c>
       <c r="E13" s="25" t="n">
-        <v>61</v>
+        <v>65.7723</v>
       </c>
       <c r="F13" s="25" t="n">
-        <v>64.5</v>
+        <v>68.6598</v>
       </c>
     </row>
     <row r="14">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="C75" s="24" t="n">
-        <v>126491.9551090501</v>
+        <v>126887.8267183633</v>
       </c>
     </row>
     <row r="76">
